--- a/artfynd/A 42243-2021 artfynd.xlsx
+++ b/artfynd/A 42243-2021 artfynd.xlsx
@@ -788,7 +788,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Robin Mårtensson, Malin Mårtensson</t>
+          <t>Malin Mårtensson , Robin Mårtensson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
